--- a/backend/data/financials_by_company/0315.HK.xlsx
+++ b/backend/data/financials_by_company/0315.HK.xlsx
@@ -3903,202 +3903,202 @@
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EX1" t="inlineStr">
@@ -4201,10 +4201,10 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>4.71</v>
+        <v>4.64</v>
       </c>
       <c r="V2" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
       <c r="W2" t="n">
         <v>4.63</v>
@@ -4213,10 +4213,10 @@
         <v>4.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.71</v>
+        <v>4.64</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
       <c r="AA2" t="n">
         <v>4.63</v>
@@ -4228,7 +4228,7 @@
         <v>0.29</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
       <c r="AE2" t="n">
         <v>1772755200</v>
@@ -4237,37 +4237,37 @@
         <v>0.7033</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.18</v>
+        <v>7.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.21</v>
+        <v>0.214</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.333334</v>
+        <v>10.173912</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.333334</v>
+        <v>10.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>764992</v>
+        <v>517139</v>
       </c>
       <c r="AL2" t="n">
-        <v>764992</v>
+        <v>517139</v>
       </c>
       <c r="AM2" t="n">
-        <v>926655</v>
+        <v>929879</v>
       </c>
       <c r="AN2" t="n">
-        <v>758025</v>
+        <v>786659</v>
       </c>
       <c r="AO2" t="n">
-        <v>758025</v>
+        <v>786659</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4276,13 +4276,13 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>5119425024</v>
+        <v>5152453120</v>
       </c>
       <c r="AU2" t="n">
-        <v>5185482040</v>
+        <v>5108415428</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.24</v>
+        <v>4.45</v>
       </c>
       <c r="AW2" t="n">
         <v>5.3</v>
@@ -4294,19 +4294,19 @@
         <v>1.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.80962604</v>
+        <v>0.8148493999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9884</v>
+        <v>4.9348</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8895</v>
+        <v>4.8852</v>
       </c>
       <c r="BC2" t="n">
         <v>0.32</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.06794055</v>
+        <v>0.06896552</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>3255947008</v>
+        <v>3288975616</v>
       </c>
       <c r="BH2" t="n">
         <v>0.07915999999999999</v>
@@ -4332,7 +4332,7 @@
         <v>0.73765</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0396</v>
+        <v>0.03271</v>
       </c>
       <c r="BM2" t="n">
         <v>1100951601</v>
@@ -4341,7 +4341,7 @@
         <v>4.897</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.949561</v>
+        <v>0.95568717</v>
       </c>
       <c r="BP2" t="n">
         <v>1751241600</v>
@@ -4359,7 +4359,7 @@
         <v>500568000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="BV2" t="n">
         <v>0.45</v>
@@ -4376,16 +4376,16 @@
         <v>1300838400</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.515</v>
+        <v>0.52</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.908</v>
+        <v>1.927</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.100467324</v>
+        <v>0.04035878</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CD2" t="n">
         <v>0.145</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="CG2" t="n">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
@@ -4501,149 +4501,149 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DJ2" t="b">
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>SMARTONE TELE</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>SmarTone Telecommunications Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.8620681</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1783066093</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>finmb_112388</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="DK2" t="n">
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.03999996</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>4.63 - 4.72</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>929879</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.23000002</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.0516854</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>4.45 - 5.3</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.62000036</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.11698119</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>4.035878</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1756724340</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1757332800</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1740578400</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>1740578400</v>
+      </c>
+      <c r="EL2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.25480032</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-0.05163336</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-0.2052002</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.042004462</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EW2" t="n">
         <v>946949400000</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.059999943</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>4.63 - 4.72</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>926655</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.41000032</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.096698195</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>4.24 - 5.3</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.6500001</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.122641526</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>10.046732</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1756724340</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1757332800</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1740578400</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1740578400</v>
-      </c>
-      <c r="DZ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.3383999</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.06783736</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.23950005</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.04898252</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>finmb_112388</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-1.2738842</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>SMARTONE TELE</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>SmarTone Telecommunications Holdings Limited</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EV2" t="n">
-        <v>1782115692</v>
-      </c>
-      <c r="EW2" t="b">
-        <v>0</v>
       </c>
       <c r="EX2" t="inlineStr"/>
     </row>
